--- a/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Matriz de Requerimientos CuTuCo.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Matriz de Requerimientos CuTuCo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignac\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignac\Videos\Inicio\Evidencias de Documentación\Documentos Actualizados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF323B2-8E40-4FE1-8DC1-B8B11E31A403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F20202-35F5-416E-9E2D-22CC97C16659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <t>Usuario (Cliente, Vendedor, Administrador); Supabase Auth (GoTrue); Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que el acceso se hace con correo y contraseña a través de Supabase Auth (GoTrue). Cuando las credenciales son correctas, Supabase entrega un JWT de acceso y un refresh token, y el sistema lee el rol del perfil (Cliente, Vendedor o Administrador) para dejar al usuario solo en el panel que le corresponde. Los permisos sobre los datos se refuerzan con políticas RLS en PostgreSQL, de modo que cada rol ve únicamente lo suyo aunque consulte directo por PostgREST. Las contraseñas las maneja Supabase Auth con hash; nosotros no las guardamos en texto plano.
+    <t>Definimos que el acceso se hace con correo y contraseña a través de Supabase Auth (GoTrue). Cuando las credenciales son correctas, Supabase entrega un JWT de acceso y un refresh token, y el sistema lee el rol del perfil (Cliente, Vendedor o Administrador) para dejar al usuario solo en el panel que le corresponde. Los permisos sobre los datos se refuerzan con políticas RLS en PostgreSQL, de modo que cada rol ve únicamente lo suyo aunque consulte directo por PostgREST. Las contraseñas las maneja Supabase Auth con hash; nosotros no las guardamos en texto plano.
 Contra la fuerza bruta usamos dos capas: Supabase Auth responde 429 cuando hay demasiados intentos, y FastAPI bloquea la cuenta durante 15 minutos al quinto intento fallido, usando los campos intentos_login_fallidos y bloqueado_hasta del perfil. No existe auto-registro como Administrador, y un Vendedor sin aprobar no accede a sus funciones de venta.
 Pruebas: CP-01 (un usuario por rol), CP-02 (cinco intentos fallidos) y CP-16 (acceso cruzado entre roles). Vicente implementa Auth, RLS y el bloqueo en FastAPI; Ignacio arma la pantalla de login y la redirección según el rol.</t>
   </si>
@@ -70,10 +70,10 @@
     <t>Gestión de Catálogo, Carrito y Compra para Cliente</t>
   </si>
   <si>
-    <t>Visitante (navegación), Cliente (compra); Transbank Webpay Plus; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
-  </si>
-  <si>
-    <t>Nosotros definimos que el Visitante puede explorar el catálogo sin iniciar sesión, usando el buscador, los filtros y la ficha de cada producto. El login se pide solo cuando quiere comprar. El Cliente agrega productos al carrito, cambia cantidades, revisa el total y sigue al checkout, donde el sistema valida el stock y la región (RF-009) y lo envía a pagar con Webpay Plus Test (RF-005). Al terminar, el pedido queda registrado, el carrito se vacía y la compra aparece en su historial de compras. El Cliente también puede ver su perfil.
+    <t>Visitante (navegación), Cliente (compra); Transbank Webpay Mall (Split Payment); Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
+  </si>
+  <si>
+    <t>Definimos que el Visitante puede explorar el catálogo sin iniciar sesión, usando el buscador, los filtros y la ficha de cada producto. El login se pide solo cuando quiere comprar. El Cliente agrega productos al carrito, cambia cantidades, revisa el total y sigue al checkout, donde el sistema valida el stock y la región (RF-009) y lo envía a pagar con Webpay Mall (Split Payment) de Transbank (RF-005). Cada compra queda asociada a la cuenta del usuario: no hay compra como invitado. En el checkout el sistema emite boleta a Consumidor Final con el RUT genérico 66.666.666-6 para personas naturales; cuando el comprador es una empresa (B2B), se solicitan RUT de empresa, razón social, giro y dirección tributaria, con autocompletado de razón social y giro desde una API pública (por ejemplo SRE/SII). Al terminar, el pedido queda registrado, el carrito se vacía y la compra aparece en su historial de compras. El Cliente también puede ver su perfil.
 En esta versión no hay historial de precios (RF-008 quedó fuera) ni geolocalización del productor. Si un producto no tiene stock suficiente o el Cliente está en otra región, el sistema bloquea la compra y explica el motivo; si el pago falla, muestra el error y deja reintentar.
 Metas de tiempo: catálogo en menos de 3 segundos y checkout en menos de 5. Pruebas: CP-04 y CP-05. Ignacio construye el flujo en Vue.js; Vicente se encarga de las consultas (PostgREST y FastAPI) y de las reglas del checkout.</t>
   </si>
@@ -87,7 +87,7 @@
     <t>Vendedor (Productor AFC); Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que el Vendedor, una vez aprobado por el Administrador, administra su tienda desde su panel: crea, consulta, edita y desactiva productos con nombre, descripción, precio, stock, categoría y una foto tomada con la cámara, que se guarda en Supabase Storage. También modifica el stock, revisa los pedidos que recibe, registra sus ventas y gestiona el delivery de sus pedidos (RF-025).
+    <t>Definimos que el Vendedor, una vez aprobado por el Administrador, administra su tienda desde su panel: crea, consulta, edita y desactiva productos con nombre, descripción, precio, stock, categoría y una foto tomada con la cámara, que se guarda en Supabase Storage. También modifica el stock, revisa los pedidos que recibe, registra sus ventas y gestiona el delivery de sus pedidos (RF-025).
 Desactivar un producto es una baja lógica (RF-017): sale del catálogo pero no se borra. Los formularios siguen las validaciones de RF-019. Un Vendedor suspendido o con ban permanente no puede vender (RF-026).
 En el alcance final no hay umbral ni alertas de stock bajo (RF-010 quedó fuera), así que el productor revisa su stock a mano; lo dejamos anotado como limitación del MVP. Tampoco pedimos fotos de evidencia del pedido: las reemplaza el código de verificación (RF-007).
 Prueba principal: CP-07 (crear, editar, desactivar, cambiar stock, enviar un dato inválido y comprar sobre el stock disponible). Ignacio hace el panel; Vicente se encarga de las reglas, la persistencia y las políticas RLS.</t>
@@ -102,7 +102,7 @@
     <t>Administrador; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que el Administrador gestiona la plataforma desde su panel: crea, consulta, actualiza y desactiva usuarios, productos y categorías, y mantiene los datos de regiones y comunas. Aprueba o rechaza las cuentas de Vendedor revisando él mismo los antecedentes antes de activarlas. Modera con una lista configurable de palabras prohibidas, que el sistema revisa con el operador LIKE, y decide qué hacer con cada coincidencia. También aplica las sanciones (RF-026) y aprueba los payouts y reembolsos (RF-005 y RF-014). El dashboard (RF-011) muestra el resultado de estas acciones.
+    <t>Definimos que el Administrador gestiona la plataforma desde su panel: crea, consulta, actualiza y desactiva usuarios, productos y categorías, y mantiene los datos de regiones y comunas. Aprueba o rechaza las cuentas de Vendedor revisando la documentación KYB (cédula o E-RUT, SII, banco y domicilio) antes de activarlas; al aprobar debe ingresar el Código de Comercio Mall (Transbank) obligatorio (ej. 597055555536), con lo que se crea la ficha en la tabla productores con rut_oficial y codigo_comercio_mall y el usuario es promovido al rol vendedor. Modera con una lista configurable de palabras prohibidas, que el sistema revisa con el operador LIKE, y decide qué hacer con cada coincidencia. También aplica las sanciones (RF-026) y gestiona los reembolsos con la pasarela (RF-005). El dashboard (RF-011) muestra el resultado de estas acciones.
 Reglas de seguridad: solo el rol Administrador entra a estas rutas; las bajas son lógicas (RF-017); el sistema bloquea la eliminación de la cuenta de Administrador y que un Administrador elimine su propia cuenta, y rechaza cambiar el correo o la contraseña de otro usuario cuando esa acción está restringida. En el alcance final hay una sola cuenta de Administrador (RF-013 quedó fuera).
 Las operaciones deben responder en menos de 5 segundos. Pruebas: CP-06, CP-11, CP-14 y CP-16. Ignacio construye el panel; Vicente los servicios y las políticas de acceso.</t>
   </si>
@@ -110,14 +110,13 @@
     <t>RF-005</t>
   </si>
   <si>
-    <t>Pago en Custodia (Escrow)</t>
-  </si>
-  <si>
-    <t>Cliente; Vendedor; Administrador; Transbank Webpay Plus; Resend; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
-  </si>
-  <si>
-    <t>Nosotros definimos que el pago se hace con Webpay Plus normal en modo de prueba (no usamos Diferido ni Mall) y que CuTuCo retiene el 100% de la venta. El flujo es: el backend crea la transacción (create), el Cliente es redirigido a Webpay, vuelve con el token_ws y el backend confirma con commit. Cada pago se guarda en la tabla payments con buy_order y token_ws únicos, para que un retorno repetido no duplique la orden ni el pago. Con el commit correcto el pedido pasa a preparación y el dinero queda retenido.
-Cuando el pedido está entregado con el código correcto, el Administrador aprueba el payout al Vendedor de forma manual. En el MVP es una simulación, no una transferencia real, y se descuentan el fee y la tarifa de delivery (RF-014). Los reembolsos post venta usan el mismo mecanismo. Para los payouts, el Vendedor registra banco, tipo y número de cuenta, y los guardamos cifrados.
+    <t>Pago con Webpay Mall (Split Payment)</t>
+  </si>
+  <si>
+    <t>Cliente; Vendedor; Administrador; Transbank Webpay Mall (Split Payment); Resend; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
+  </si>
+  <si>
+    <t>Definimos que el pago se realiza con Webpay Mall (Split Payment) de Transbank en ambiente de integración. La pasarela realiza la captura y la dispersión en tiempo real y deposita directo en la cuenta bancaria del comercio, por lo que CuTuCo no retiene saldos ni ejecuta payouts: quedan eliminados la custodia de fondos y el motor de transferencias propias. El flujo técnico se mantiene: el backend crea la transacción (create), el Cliente es redirigido a Webpay, vuelve con el token_ws y el backend confirma con commit. Cada pago se guarda en la tabla payments con buy_order y token_ws únicos, para que un retorno repetido no duplique la orden ni el pago. Con el commit correcto el pedido pasa a preparación y la pasarela ejecuta la dispersión (Split Payment), donde se descuentan el fee y la tarifa de delivery (RF-014). Los reembolsos post venta se gestionan con la pasarela. La cuenta bancaria de destino se inscribe en Transbank y se valida con el certificado de titularidad bancaria (RF-021); los datos bancarios que se almacenan se guardan cifrados.
 Si el commit falla o el token_ws no corresponde, el sistema no marca el pago como completado y permite reintentar sin duplicar. Si Transbank no está disponible, usamos mocks o stubs para no frenar el avance y repetimos la prueba real después. El commit debe tardar menos de 5 segundos.
 Pruebas: CP-08 a CP-11 y CP-17. Vicente implementa el flujo y el manejo de secretos (Secret Manager); Ignacio, el checkout y el retorno en la interfaz.</t>
   </si>
@@ -131,7 +130,7 @@
     <t>Cliente; Vendedor; Administrador; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos una calificación simple: el Cliente califica con una nota de 1 a 5 al recibir su pedido y el sistema calcula el promedio por Vendedor. Reemplaza al score de reputación con ponderaciones 40/40/20 del ERS inicial. Con este cambio ya no hay pausa automática por score ni sello "Cosecha del día"; cualquier sanción la decide el Administrador a mano (RF-026).
+    <t>Definimos una calificación simple: el Cliente califica con una nota de 1 a 5 al recibir su pedido y el sistema calcula el promedio por Vendedor. Reemplaza al score de reputación con ponderaciones 40/40/20 del ERS inicial. Con este cambio ya no hay pausa automática por score ni sello "Cosecha del día"; cualquier sanción la decide el Administrador a mano (RF-026).
 La probamos con notas en los extremos (1 y 5) y comprobando que el promedio salga bien (CP-14). Vicente implementa el cálculo y la persistencia; Ignacio, la pantalla donde el Cliente califica.</t>
   </si>
   <si>
@@ -144,7 +143,7 @@
     <t>Vendedor; Cliente; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos un código de verificación por pedido que respalda la entrega. Se guarda en delivery_tracking y el Vendedor lo ingresa al momento de entregar: el pedido solo pasa a Entregado si el código es correcto; un código incorrecto se rechaza y el pedido no cambia de estado.
+    <t>Definimos un código de verificación por pedido que respalda la entrega. Se guarda en delivery_tracking y el Vendedor lo ingresa al momento de entregar: el pedido solo pasa a Entregado si el código es correcto; un código incorrecto se rechaza y el pedido no cambia de estado.
 Este código reemplaza las dos fotografías obligatorias (al armar y al entregar) del ERS inicial, que sacamos del alcance para bajar la complejidad. Sin fotos tenemos menos respaldo visual ante una disputa; lo aceptamos y lo dejamos registrado como riesgo.
 Pruebas: CP-12 y CP-17, con código correcto, incorrecto y repetido. Vicente genera y valida el código en el backend; Ignacio hace el campo de ingreso en el panel del Vendedor.</t>
   </si>
@@ -173,7 +172,7 @@
     <t>Cliente; Vendedor; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que la compra solo avanza si el Cliente y el productor están en la misma región. En el checkout, el sistema compara la región del Cliente con la del productor (id_region): si coinciden, la compra continúa; si no, la bloquea e informa el motivo.
+    <t>Definimos que la compra solo avanza si el Cliente y el productor están en la misma región. En el checkout, el sistema compara la región del Cliente con la del productor (id_region): si coinciden, la compra continúa; si no, la bloquea e informa el motivo.
 En el alcance final validamos solo por región. No usamos geolocalización de Google, ni restricción por comuna, ni cálculo de rutas. La validación debe ejecutarse en menos de 2 segundos.
 Prueba: CP-13 (misma región y regiones distintas). Vicente implementa la regla en el backend; Ignacio muestra el bloqueo y el mensaje en el checkout.</t>
   </si>
@@ -196,7 +195,7 @@
     <t>Dashboard Administrativo</t>
   </si>
   <si>
-    <t>Nosotros definimos un dashboard solo para el Administrador, reducido a lo que necesita para operar: ver y resolver aprobaciones de productores, sanciones, payouts y reembolsos, junto con las métricas básicas de transacciones (finalizadas, pendientes y rechazadas) y comisiones. En esta versión sacamos las ventas por región y el ticket promedio.
+    <t>Definimos un dashboard solo para el Administrador, reducido a lo que necesita para operar: ver y resolver aprobaciones de productores, sanciones y reembolsos, junto con las métricas básicas de transacciones (finalizadas, pendientes y rechazadas) y comisiones. En esta versión sacamos las ventas por región y el ticket promedio.
 Si no hay datos, el dashboard muestra ceros o el mensaje "No se ha encontrado información", para no dejar campos ambiguos. Las métricas iniciales deben cargar en menos de 5 segundos.
 Pruebas: CP-06, CP-14 y CP-17 (por ejemplo, que la aprobación de un Vendedor se refleje en el dashboard). Ignacio construye la vista; Vicente las consultas.</t>
   </si>
@@ -210,7 +209,7 @@
     <t>Sistema; Resend; Supabase Auth; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos dos vías de envío, ambas con Resend. Los correos de autenticación (bienvenida, verificación de cuenta y recuperación de contraseña) los envía Supabase Auth a través del SMTP de Resend. Los correos del negocio (pago retenido, aprobación o rechazo de productor, payout y reembolso) los envía FastAPI con la API de Resend. Ya no hay avisos de stock bajo (RF-010 quedó fuera) y dejamos de lado la idea inicial de usar smtplib o fastapi-mail.
+    <t>Definimos dos vías de envío, ambas con Resend. Los correos de autenticación (bienvenida, verificación de cuenta y recuperación de contraseña) los envía Supabase Auth a través del SMTP de Resend. Los correos del negocio (confirmación de pago, aprobación o rechazo de productor y reembolso) los envía FastAPI con la API de Resend. Ya no hay avisos de stock bajo (RF-010 quedó fuera) y dejamos de lado la idea inicial de usar smtplib o fastapi-mail.
 Usamos plantillas para mantener un formato parecido entre notificaciones. Si un envío falla, el sistema reintenta y registra el error en el log. El correo debe salir en menos de 10 segundos en condiciones normales.
 Pruebas: CP-03 y CP-15, con casillas de prueba para recibir cada correo. Vicente configura Resend y los envíos desde el backend; Ignacio, los mensajes que ve el usuario en la interfaz.</t>
   </si>
@@ -233,9 +232,9 @@
     <t>Administrador; Vendedor; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que CuTuCo retiene el 100% de la venta y que, cuando el pedido está entregado, el Administrador aprueba el payout manual al Vendedor descontando dos cosas: un fee base de 5% y una tarifa fija de delivery de 3.500 CLP. El fee se revisará según el flujo de caja. El monto neto que recibe el Vendedor es la venta menos esos descuentos, y el cálculo queda guardado en la tabla payouts.
-La suscripción mensual no entra en el MVP: la dejamos como evaluación para una futura Opción B. En el MVP el payout es una simulación manual y el Administrador no puede pagar dos veces el mismo pedido.
-Pruebas: CP-10 y CP-11 (monto neto correcto y payout sin duplicados). Vicente implementa el cálculo y la tabla; Ignacio muestra los montos en el panel de administración y en el del Vendedor.</t>
+    <t>Definimos que la liquidación la realiza la pasarela vía Split Payment: del total de la venta se descuentan un fee base de 5% y una tarifa fija de delivery de 3.500 CLP, y el resto se dispersa directo a la cuenta bancaria del comercio. El fee se revisará según el flujo de caja. CuTuCo no retiene la venta ni ejecuta payouts manuales: la dispersión la realiza Transbank al momento del pago. La cuenta bancaria de destino se inscribe en Transbank y se valida con el certificado de titularidad bancaria (RF-021).
+La suscripción mensual no entra en el MVP: la dejamos como evaluación para una futura Opción B. Una misma liquidación no puede registrarse dos veces para el mismo pago.
+Pruebas: CP-10 y CP-11 (neto dispersado correcto y liquidación sin duplicados). Vicente implementa el cálculo y su registro; Ignacio muestra los montos en el panel de administración y en el del Vendedor.</t>
   </si>
   <si>
     <t>RF-015</t>
@@ -268,7 +267,7 @@
     <t>Eliminación Lógica (Soft Delete) y Cascada</t>
   </si>
   <si>
-    <t>Nosotros definimos que las eliminaciones que hace el Administrador son lógicas. El sistema cambia el estado del registro a deshabilitado y, cuando la baja afecta a registros relacionados, los reasigna en cascada. Nunca hacemos DELETE físico en la base de datos para este tipo de operaciones, así el historial sigue disponible para métricas y pagos.
+    <t>Definimos que las eliminaciones que hace el Administrador son lógicas. El sistema cambia el estado del registro a deshabilitado y, cuando la baja afecta a registros relacionados, los reasigna en cascada. Nunca hacemos DELETE físico en la base de datos para este tipo de operaciones, así el historial sigue disponible para métricas y pagos.
 Por ejemplo, un producto desactivado sale del catálogo pero se conserva. Si el registro está protegido por una regla de seguridad (como la cuenta de Administrador), el sistema bloquea la operación y no cambia nada. La desactivación debe completarse en menos de 3 segundos.
 Se prueba junto a RF-018 y RF-019 en CP-07. Vicente implementa la lógica y las restricciones en PostgreSQL; Ignacio, las acciones de desactivar en los paneles.</t>
   </si>
@@ -279,7 +278,7 @@
     <t>Combobox para Claves Foráneas</t>
   </si>
   <si>
-    <t>Nosotros definimos que las tablas de consulta (categorías, regiones y comunas) y las claves foráneas que el usuario debe elegir se muestran como combobox en los formularios. El usuario selecciona un valor que ya existe en lugar de escribir una referencia a mano, y así evitamos relaciones inválidas. La selección es obligatoria al enviar el formulario y, si la tabla no tiene datos, el combobox aparece vacío.
+    <t>Definimos que las tablas de consulta (categorías, regiones y comunas) y las claves foráneas que el usuario debe elegir se muestran como combobox en los formularios. El usuario selecciona un valor que ya existe en lugar de escribir una referencia a mano, y así evitamos relaciones inválidas. La selección es obligatoria al enviar el formulario y, si la tabla no tiene datos, el combobox aparece vacío.
 Los valores salen de consultas directas a PostgREST. Se comprueba junto a RF-017 y RF-019 en CP-07. Ignacio construye los componentes en Vue.js; Vicente expone las consultas y deja cargados los datos de prueba (regiones, comunas y categorías).</t>
   </si>
   <si>
@@ -292,7 +291,7 @@
     <t>Cliente; Vendedor; Administrador; Visitante; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos tres capas de validación. La principal está en el frontend con Vuelidate (Vue.js) y detecta errores antes de enviar el formulario, con mensajes claros. En el backend dejamos una validación mínima con Pydantic en FastAPI, para que la API no acepte datos inválidos aunque se salten el navegador. La última barrera son las restricciones de la base de datos (tipos, UNIQUE, claves foráneas). Para los formatos usamos expresiones regulares definidas en una matriz de validaciones, de modo que los criterios sean los mismos en todos los formularios.
+    <t>Definimos tres capas de validación. La principal está en el frontend con Vuelidate (Vue.js) y detecta errores antes de enviar el formulario, con mensajes claros. En el backend dejamos una validación mínima con Pydantic en FastAPI, para que la API no acepte datos inválidos aunque se salten el navegador. La última barrera son las restricciones de la base de datos (tipos, UNIQUE, claves foráneas). Para los formatos usamos expresiones regulares definidas en una matriz de validaciones, de modo que los criterios sean los mismos en todos los formularios.
 Elegimos no duplicar toda la lógica en el backend porque es un MVP de dos personas. Se verifica con CP-07 y con NF-03 (datos inválidos en formulario, endpoints críticos y base). Ignacio lidera las reglas del frontend; Vicente, las del backend y la base de datos.</t>
   </si>
   <si>
@@ -305,7 +304,7 @@
     <t>Visitante (futuro Cliente); Supabase Auth; Resend; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que el registro de Cliente pide nombre, apellidos, correo electrónico único, contraseña con confirmación, región y comuna. El sistema valida la política de contraseña en el frontend y en el backend, crea la cuenta en Supabase Auth y asigna únicamente el rol Cliente; un visitante no puede registrarse como Vendedor ni como Administrador por este formulario. Los correos de bienvenida y verificación salen por el SMTP de Resend (RF-012).
+    <t>Definimos que el registro de Cliente pide nombre, apellidos, correo electrónico único, contraseña con confirmación, región y comuna. El sistema valida la política de contraseña en el frontend y en el backend, crea la cuenta en Supabase Auth y asigna únicamente el rol Cliente; un visitante no puede registrarse como Vendedor ni como Administrador por este formulario. Los correos de bienvenida y verificación salen por el SMTP de Resend (RF-012).
 Si el correo ya existe, el sistema rechaza el registro y pide usar otro. Si la contraseña no cumple la política, informa qué regla falta y no crea la cuenta. Una vez superadas las validaciones, la creación debe tardar menos de 5 segundos.
 Prueba: CP-03. Ignacio hace el formulario con Vuelidate; Vicente configura Supabase Auth y el perfil asociado.</t>
   </si>
@@ -319,7 +318,7 @@
     <t>Visitante (futuro Vendedor); Administrador; Resend; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que el registro de Vendedor pide datos personales, datos de la tienda, región y comuna, y los datos bancarios para los payouts (banco, tipo y número de cuenta), que guardamos cifrados. En el alcance final no pedimos el carnet. La cuenta se crea en estado pendiente de aprobación y no puede vender hasta que el Administrador revise los antecedentes y la apruebe o la rechace. Si la rechaza, queda registrado el motivo y se avisa por correo (RF-012). La aprobación manual es un paso obligatorio del MVP.
+    <t>Definimos que el registro de Vendedor pide datos personales, datos de la tienda, región y comuna, los datos bancarios de destino (banco, tipo y número de cuenta) que se inscriben en Transbank y se guardan cifrados, y la documentación de verificación KYB según el tipo de persona. Si el Vendedor es Persona Natural (comerciante o agricultor individual): copia de la cédula de identidad, Certificado de Inicio de Actividades (SII), Certificado de Titularidad Bancaria y comprobante de domicilio o predio. Si el Vendedor es Persona Jurídica (empresa, SpA, cooperativa, Ltda.): E-RUT de la empresa, cédula del representante legal, Certificado de Titularidad Bancaria de la empresa y comprobante de domicilio tributario o predio. Los documentos se almacenan de forma continua en Storage de la postulación. La cuenta se crea en estado pendiente de aprobación y no puede vender hasta que el Administrador revise la documentación y la apruebe o la rechace. Al aprobar, la UI exige ingresar el Código de Comercio Mall (Transbank) obligatorio (ej. 597055555536): la postulación queda aprobada, se crea la ficha en la tabla productores con rut_oficial y codigo_comercio_mall y el usuario es promovido al rol vendedor. Si la rechaza, queda registrado el motivo y se avisa por correo (RF-012). La aprobación manual es un paso obligatorio del MVP.
 Como la revisión es humana, es un control que tenemos que cuidar; lo dejamos incluido en los riesgos del proyecto.
 Prueba: CP-06 (cuenta pendiente, sin acceso a ventas hasta ser aprobada, y reflejo del cambio de estado en el dashboard). Ignacio hace el formulario y la vista de aprobación; Vicente, el estado de la cuenta, el cifrado y los correos.</t>
   </si>
@@ -333,7 +332,7 @@
     <t>Visitante; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos una navegación pública que permite ver el catálogo, los precios y el detalle de los productos sin iniciar sesión. La autenticación solo se exige cuando el Visitante intenta pasar a una compra o checkout; no existe checkout sin sesión. Si no tiene cuenta, puede registrarse como Cliente (RF-020) y volver al proceso de compra. En esta versión no se muestra historial de precios (RF-008 quedó fuera).
+    <t>Definimos una navegación pública que permite ver el catálogo, los precios y el detalle de los productos sin iniciar sesión. La autenticación solo se exige cuando el Visitante intenta pasar a una compra o checkout; no existe checkout sin sesión. Si no tiene cuenta, puede registrarse como Cliente (RF-020) y volver al proceso de compra. En esta versión no se muestra historial de precios (RF-008 quedó fuera).
 El catálogo público debe cargar en menos de 3 segundos. Prueba: CP-04. Ignacio construye la navegación en Vue.js; Vicente deja las consultas públicas del catálogo protegidas con RLS para que un visitante solo lea datos públicos.</t>
   </si>
   <si>
@@ -346,7 +345,7 @@
     <t>Cliente; Vendedor; Administrador; Supabase Auth; Resend; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que la recuperación se hace con el correo registrado, usando Supabase Auth. El sistema recibe la solicitud y responde siempre con un mensaje genérico, exista o no el correo, para no revelar qué cuentas existen. Envía un enlace con un token de un solo uso, que sirve durante 30 minutos para crear una nueva contraseña. Si se genera un token nuevo, el anterior deja de valer. Al terminar el cambio, el sistema actualiza el hash y los tokens anteriores quedan invalidados. El correo sale por el SMTP de Resend y debe enviarse en menos de 10 segundos.
+    <t>Definimos que la recuperación se hace con el correo registrado, usando Supabase Auth. El sistema recibe la solicitud y responde siempre con un mensaje genérico, exista o no el correo, para no revelar qué cuentas existen. Envía un enlace con un token de un solo uso, que sirve durante 30 minutos para crear una nueva contraseña. Si se genera un token nuevo, el anterior deja de valer. Al terminar el cambio, el sistema actualiza el hash y los tokens anteriores quedan invalidados. El correo sale por el SMTP de Resend y debe enviarse en menos de 10 segundos.
 Si el token venció o ya se usó, el sistema rechaza el enlace y pide iniciar la recuperación de nuevo. Prueba: CP-03. Vicente configura Supabase Auth y Resend; Ignacio hace las pantallas de solicitud y de nueva contraseña.</t>
   </si>
   <si>
@@ -359,7 +358,7 @@
     <t>Cliente; Vendedor; Administrador; Supabase Auth; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que el cambio de contraseña se hace desde Mi perfil y pide la contraseña actual, la nueva y su confirmación. El sistema aplica la política de contraseña, guarda el nuevo hash a través de Supabase Auth e invalida las sesiones y refresh tokens existentes, así que el usuario debe iniciar sesión otra vez. El correo no se puede cambiar desde este formulario.
+    <t>Definimos que el cambio de contraseña se hace desde Mi perfil y pide la contraseña actual, la nueva y su confirmación. El sistema aplica la política de contraseña, guarda el nuevo hash a través de Supabase Auth e invalida las sesiones y refresh tokens existentes, así que el usuario debe iniciar sesión otra vez. El correo no se puede cambiar desde este formulario.
 Si la contraseña actual no coincide, o la nueva no cumple la política o no coincide con su confirmación, el sistema muestra el error y no guarda nada. La actualización debe tardar menos de 3 segundos. Prueba: CP-03. Ignacio hace el formulario; Vicente, la validación y la invalidación de sesiones.</t>
   </si>
   <si>
@@ -372,8 +371,8 @@
     <t>Vendedor (Productor); Cliente; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que en el MVP el mismo productor se encarga del delivery. El Vendedor avanza el pedido por los estados Preparación -&gt; En Tránsito -&gt; Entregado, y para marcarlo Entregado debe ingresar el código de verificación correcto (RF-007). El Cliente ve el estado en un seguimiento web dentro de la plataforma. No hay mapa, GPS en tiempo real ni fotos de evidencia. Si no hay una actualización nueva, el Cliente ve el último estado registrado.
-El pedido debe estar pagado y retenido para entrar a este flujo. El costo del delivery es la tarifa fija de 3.500 CLP más el fee (RF-014). El dinero no se libera al Vendedor al entregar: el Administrador aprueba el payout después (RF-005). Si una entrega no se completa, se gestiona como reembolso post venta.
+    <t>Definimos que en el MVP el mismo productor se encarga del delivery. El Vendedor avanza el pedido por los estados Preparación -&gt; En Tránsito -&gt; Entregado, y para marcarlo Entregado debe ingresar el código de verificación correcto (RF-007). El Cliente ve el estado en un seguimiento web dentro de la plataforma. No hay mapa, GPS en tiempo real ni fotos de evidencia. Si no hay una actualización nueva, el Cliente ve el último estado registrado.
+El pedido debe estar pagado para entrar a este flujo. El costo del delivery es la tarifa fija de 3.500 CLP más el fee (RF-014). La dispersión al comercio la realiza la pasarela al momento del pago vía Split Payment, por lo que no hay liberación posterior ni aprobación de payout (RF-005). Si una entrega no se completa, se gestiona como reembolso post venta.
 Cada cambio de estado debe reflejarse en menos de 2 segundos (p95). Pruebas: CP-12 y CP-17 (orden de los estados y código incorrecto). Ignacio construye el seguimiento y el panel del Vendedor; Vicente, los estados y la tabla delivery_tracking.</t>
   </si>
   <si>
@@ -386,7 +385,7 @@
     <t>Administrador; Vendedor; Sistema; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos que las sanciones son manuales y las aplica el Administrador desde su panel. El sistema revisa los textos de los productos y tiendas con la lista de palabras prohibidas (operador LIKE) y avisa la coincidencia; el Administrador decide si amonesta. El sistema lleva el conteo de amonestaciones con su duración, y el Administrador puede suspender al Vendedor o aplicar un Ban Permanente con un botón. Un Vendedor suspendido o baneado no puede vender.
+    <t>Definimos que las sanciones son manuales y las aplica el Administrador desde su panel. El sistema revisa los textos de los productos y tiendas con la lista de palabras prohibidas (operador LIKE) y avisa la coincidencia; el Administrador decide si amonesta. El sistema lleva el conteo de amonestaciones con su duración, y el Administrador puede suspender al Vendedor o aplicar un Ban Permanente con un botón. Un Vendedor suspendido o baneado no puede vender.
 Con la versión final quedan fuera la pausa automática por score de reputación y la suspensión automática por acumulación de amonestaciones: no hay reglas automáticas, cada caso lo resolvemos a mano.
 Prueba: CP-14 (texto con palabra prohibida, amonestaciones, suspensión, ban permanente y bloqueo del Vendedor). Vicente implementa las reglas y el registro; Ignacio, la vista de sanciones del panel.</t>
   </si>
@@ -403,7 +402,7 @@
     <t>Sistema; Administrador; Cliente; Vendedor; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos cuatro exigencias de seguridad y calidad de datos. Primera, acceso: los tokens expiran, cada rol solo accede a lo suyo y las políticas RLS protegen los datos tanto por la API como por PostgREST directo. Segunda, integridad: buy_order y token_ws son únicos, y un reintento no puede generar pagos ni payouts duplicados. Tercera, validación: la API y la base de datos rechazan entradas inválidas con una respuesta controlada. Cuarta, datos financieros: banco, tipo y número de cuenta del Vendedor se guardan cifrados, los ve solo el rol autorizado y no deben aparecer en texto plano en la base, en los logs ni en las respuestas.
+    <t>Definimos cuatro exigencias de seguridad y calidad de datos. Primera, acceso: los tokens expiran, cada rol solo accede a lo suyo y las políticas RLS protegen los datos tanto por la API como por PostgREST directo. Segunda, integridad: buy_order y token_ws son únicos, y un reintento no puede generar pagos ni liquidaciones duplicados. Tercera, validación: la API y la base de datos rechazan entradas inválidas con una respuesta controlada. Cuarta, datos financieros: los datos bancarios que se almacenan se guardan cifrados, los ve solo el rol autorizado y no deben aparecer en texto plano en la base, en los logs ni en las respuestas.
 Las credenciales (Webpay, API key de Resend y la clave de cifrado) van en GCP Secret Manager o variables de entorno, nunca en el repositorio.
 Pruebas: NF-01, NF-02, NF-03, NF-04 y CP-16. Vicente lidera la implementación; Ignacio revisa que el frontend no exponga datos ni claves.</t>
   </si>
@@ -417,7 +416,7 @@
     <t>Sistema; Cliente; Visitante; Responsables de desarrollo: Vicente Rivera (Líder backend) e Ignacio Fuenzalida (IT frontend).</t>
   </si>
   <si>
-    <t>Nosotros definimos tiempos máximos para los puntos que más pesan en la experiencia de compra: catálogo en menos de 3 segundos, checkout en menos de 5 segundos y tx.commit de Webpay en menos de 5 segundos. Los demás requerimientos mantienen sus propias metas del ERS (por ejemplo, correos en menos de 10 segundos y cambios de estado del delivery en menos de 2 segundos).
+    <t>Definimos tiempos máximos para los puntos que más pesan en la experiencia de compra: catálogo en menos de 3 segundos, checkout en menos de 5 segundos y tx.commit de Webpay en menos de 5 segundos. Los demás requerimientos mantienen sus propias metas del ERS (por ejemplo, correos en menos de 10 segundos y cambios de estado del delivery en menos de 2 segundos).
 Las mediciones las hacemos en las pruebas y, si hay desviaciones, las registramos para analizarlas después. Prueba: NF-05. Ignacio mide el comportamiento del frontend; Vicente, el de la API, la base de datos y Webpay.</t>
   </si>
 </sst>
@@ -797,7 +796,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
+  <sheetPr filterMode="1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:Z999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2381,13 +2382,14 @@
     <row r="998" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="12.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:F29" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="5">
       <filters>
         <filter val="Por hacer"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="18" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>